--- a/Python advanced/pandas/report.xlsx
+++ b/Python advanced/pandas/report.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,6 +594,66 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Eve</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>raju@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>rani@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Eve</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>raju@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>rani@gmail.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
